--- a/excel_results/source.xlsx
+++ b/excel_results/source.xlsx
@@ -22635,7 +22635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22655,13 +22655,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -22669,20 +22684,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>9.282258064516126</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>9.037419354838711</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.348387096774195</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.860645161290322</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>3.285666666666667</v>
       </c>
     </row>
@@ -22691,69 +22717,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>7.938387096774193</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>8.129354838709679</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>7.260937499999998</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.623500000000001</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>2.7678125</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.129354838709679</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
+        <v>9.282258064516126</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.938387096774193</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>6.58225806451613</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>3.936774193548386</v>
+      </c>
+      <c r="M4" t="n">
         <v>2.777096774193549</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>3.936774193548386</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.936774193548386</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.623500000000001</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.860645161290322</v>
+        <v>9.037419354838711</v>
       </c>
     </row>
     <row r="6">
@@ -22761,25 +22799,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>2.777096774193549</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
         <v>6.58225806451613</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.260937499999998</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8.348387096774195</v>
       </c>
     </row>
     <row r="7">
@@ -22787,21 +22813,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>8.129354838709679</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>9.037419354838711</v>
+        <v>7.260937499999998</v>
       </c>
     </row>
     <row r="8">
@@ -22809,59 +22827,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>7.260937499999998</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7.938387096774193</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8.129354838709679</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>8.348387096774195</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>4.623500000000001</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.282258064516126</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>3.936774193548386</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>2.7678125</v>
+        <v>4.623500000000001</v>
       </c>
     </row>
     <row r="11">
@@ -22869,13 +22869,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>9.037419354838711</v>
+        <v>5.860645161290322</v>
       </c>
     </row>
     <row r="12">
@@ -22883,13 +22883,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>8.348387096774195</v>
+        <v>2.777096774193549</v>
       </c>
     </row>
     <row r="13">
@@ -22897,13 +22897,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>5.860645161290322</v>
+        <v>2.7678125</v>
       </c>
     </row>
     <row r="14">
@@ -22911,10 +22911,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>3.285666666666667</v>
@@ -22931,7 +22931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22957,7 +22957,31 @@
         <v>0.76</v>
       </c>
       <c r="J1" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L1" s="1" t="n">
         <v>1.03</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -22968,10 +22992,10 @@
         <v>0.51</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="D2" t="n">
-        <v>41.31935483870968</v>
+        <v>500</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1.5</v>
@@ -22980,22 +23004,28 @@
       <c r="I2" t="n">
         <v>500</v>
       </c>
-      <c r="J2" t="n">
-        <v>22.60666666666667</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>28.5225806451613</v>
+        <v>500</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1.44</v>
@@ -23003,169 +23033,213 @@
       <c r="H3" t="n">
         <v>500</v>
       </c>
-      <c r="I3" t="n">
-        <v>31.57812500000001</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>25.5258064516129</v>
+        <v>500</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
-        <v>37.45483870967742</v>
-      </c>
+        <v>1.03</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>55.53870967741936</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31.54193548387097</v>
+      </c>
+      <c r="O4" t="n">
+        <v>18.55806451612903</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>22.60666666666667</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.51</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
       <c r="D5" t="n">
-        <v>30.54838709677419</v>
+        <v>41.31935483870968</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>30.54838709677419</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25.21333333333332</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18.55806451612903</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>500</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>37.45483870967742</v>
+        <v>28.5225806451613</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>25.5258064516129</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>23.759375</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31.54193548387097</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.51</v>
+        <v>0.99</v>
       </c>
       <c r="C7" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>29.5032258064516</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>55.53870967741936</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>29.5032258064516</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>23.759375</v>
+      </c>
+      <c r="O7" t="n">
+        <v>25.21333333333332</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>31.57812500000001</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="D8" t="n">
         <v>500</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>41.31935483870968</v>
+      </c>
+      <c r="K8" t="n">
         <v>28.5225806451613</v>
       </c>
-      <c r="I8" t="n">
-        <v>29.5032258064516</v>
-      </c>
-      <c r="J8" t="n">
-        <v>500</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>25.5258064516129</v>
+      </c>
+      <c r="O8" t="n">
+        <v>30.54838709677419</v>
+      </c>
+      <c r="P8" t="n">
+        <v>37.45483870967742</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="D9" t="n">
-        <v>29.5032258064516</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>41.31935483870968</v>
-      </c>
-      <c r="I9" t="n">
-        <v>500</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>55.53870967741936</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C10" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D10" t="n">
-        <v>23.759375</v>
+        <v>25.5258064516129</v>
       </c>
     </row>
     <row r="11">
@@ -23173,13 +23247,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.32</v>
-      </c>
       <c r="D11" t="n">
-        <v>25.21333333333332</v>
+        <v>23.759375</v>
       </c>
     </row>
     <row r="12">
@@ -23187,13 +23261,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="D12" t="n">
-        <v>31.57812500000001</v>
+        <v>31.54193548387097</v>
       </c>
     </row>
     <row r="13">
@@ -23201,13 +23275,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="D13" t="n">
-        <v>500</v>
+        <v>30.54838709677419</v>
       </c>
     </row>
     <row r="14">
@@ -23215,13 +23289,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="C14" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="D14" t="n">
-        <v>500</v>
+        <v>25.21333333333332</v>
       </c>
     </row>
     <row r="15">
@@ -23229,13 +23303,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.03</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D15" t="n">
-        <v>55.53870967741936</v>
+        <v>18.55806451612903</v>
       </c>
     </row>
     <row r="16">
@@ -23243,13 +23317,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C16" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D16" t="n">
-        <v>31.54193548387097</v>
+        <v>37.45483870967742</v>
       </c>
     </row>
     <row r="17">
@@ -23257,13 +23331,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C17" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D17" t="n">
-        <v>18.55806451612903</v>
+        <v>31.57812500000001</v>
       </c>
     </row>
     <row r="18">
@@ -23271,10 +23345,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>22.60666666666667</v>
@@ -23291,7 +23365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23311,13 +23385,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -23325,20 +23414,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>44.48709677419354</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>30.37096774193548</v>
+      </c>
+      <c r="K2" t="n">
+        <v>36.55645161290323</v>
+      </c>
+      <c r="L2" t="n">
+        <v>49.12580645161292</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>61.88333333333333</v>
       </c>
     </row>
@@ -23347,69 +23447,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>57.40967741935484</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>38.7241935483871</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>46.53124999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65.90833333333333</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>76.41250000000001</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>38.7241935483871</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
+        <v>44.48709677419354</v>
+      </c>
+      <c r="I4" t="n">
+        <v>57.40967741935484</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>70.76129032258065</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>91.9709677419355</v>
+      </c>
+      <c r="M4" t="n">
         <v>99.20645161290322</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>91.9709677419355</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>91.9709677419355</v>
-      </c>
-      <c r="I5" t="n">
-        <v>65.90833333333333</v>
-      </c>
-      <c r="J5" t="n">
-        <v>49.12580645161292</v>
+        <v>30.37096774193548</v>
       </c>
     </row>
     <row r="6">
@@ -23417,25 +23529,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>99.20645161290322</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
         <v>70.76129032258065</v>
-      </c>
-      <c r="I6" t="n">
-        <v>46.53124999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36.55645161290323</v>
       </c>
     </row>
     <row r="7">
@@ -23443,21 +23543,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>38.7241935483871</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>30.37096774193548</v>
+        <v>46.53124999999999</v>
       </c>
     </row>
     <row r="8">
@@ -23465,59 +23557,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>46.53124999999999</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
-        <v>57.40967741935484</v>
-      </c>
-      <c r="I8" t="n">
-        <v>38.7241935483871</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>36.55645161290323</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>65.90833333333333</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>44.48709677419354</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>91.9709677419355</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>76.41250000000001</v>
+        <v>65.90833333333333</v>
       </c>
     </row>
     <row r="11">
@@ -23525,13 +23599,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>30.37096774193548</v>
+        <v>49.12580645161292</v>
       </c>
     </row>
     <row r="12">
@@ -23539,13 +23613,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>36.55645161290323</v>
+        <v>99.20645161290322</v>
       </c>
     </row>
     <row r="13">
@@ -23553,13 +23627,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>49.12580645161292</v>
+        <v>76.41250000000001</v>
       </c>
     </row>
     <row r="14">
@@ -23567,10 +23641,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>61.88333333333333</v>
@@ -23587,7 +23661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23607,13 +23681,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -23621,20 +23710,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>3.396774193548387</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>3.167741935483871</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.148387096774193</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.783870967741936</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>1.913333333333332</v>
       </c>
     </row>
@@ -23643,69 +23743,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>2.429032258064516</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>2.332258064516129</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>2.537500000000001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.453333333333336</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>2.471875</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.332258064516129</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
+        <v>3.396774193548387</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.429032258064516</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>2.335483870967741</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>2.496774193548387</v>
+      </c>
+      <c r="M4" t="n">
         <v>2.645161290322581</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>2.496774193548387</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.496774193548387</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.453333333333336</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.783870967741936</v>
+        <v>3.167741935483871</v>
       </c>
     </row>
     <row r="6">
@@ -23713,25 +23825,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>2.645161290322581</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
         <v>2.335483870967741</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.537500000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.148387096774193</v>
       </c>
     </row>
     <row r="7">
@@ -23739,21 +23839,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>2.332258064516129</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>3.167741935483871</v>
+        <v>2.537500000000001</v>
       </c>
     </row>
     <row r="8">
@@ -23761,59 +23853,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>2.537500000000001</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.429032258064516</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.332258064516129</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>2.148387096774193</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>2.453333333333336</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.396774193548387</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>2.496774193548387</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>2.471875</v>
+        <v>2.453333333333336</v>
       </c>
     </row>
     <row r="11">
@@ -23821,13 +23895,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>3.167741935483871</v>
+        <v>1.783870967741936</v>
       </c>
     </row>
     <row r="12">
@@ -23835,13 +23909,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>2.148387096774193</v>
+        <v>2.645161290322581</v>
       </c>
     </row>
     <row r="13">
@@ -23849,13 +23923,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>1.783870967741936</v>
+        <v>2.471875</v>
       </c>
     </row>
     <row r="14">
@@ -23863,10 +23937,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>1.913333333333332</v>
@@ -23883,7 +23957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23903,13 +23977,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -23917,20 +24006,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>47.88387096774193</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>33.53870967741936</v>
+      </c>
+      <c r="K2" t="n">
+        <v>38.70483870967742</v>
+      </c>
+      <c r="L2" t="n">
+        <v>50.90967741935484</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>63.79666666666665</v>
       </c>
     </row>
@@ -23939,69 +24039,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>59.83870967741935</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>41.0564516129032</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>49.06875</v>
+      </c>
+      <c r="L3" t="n">
+        <v>68.36166666666668</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>78.88437499999999</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>41.0564516129032</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
+        <v>47.88387096774193</v>
+      </c>
+      <c r="I4" t="n">
+        <v>59.83870967741935</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>73.0967741935484</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>94.46774193548387</v>
+      </c>
+      <c r="M4" t="n">
         <v>101.8516129032258</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>94.46774193548387</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>94.46774193548387</v>
-      </c>
-      <c r="I5" t="n">
-        <v>68.36166666666668</v>
-      </c>
-      <c r="J5" t="n">
-        <v>50.90967741935484</v>
+        <v>33.53870967741936</v>
       </c>
     </row>
     <row r="6">
@@ -24009,25 +24121,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>101.8516129032258</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
         <v>73.0967741935484</v>
-      </c>
-      <c r="I6" t="n">
-        <v>49.06875</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38.70483870967742</v>
       </c>
     </row>
     <row r="7">
@@ -24035,21 +24135,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>41.0564516129032</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>33.53870967741936</v>
+        <v>49.06875</v>
       </c>
     </row>
     <row r="8">
@@ -24057,59 +24149,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>49.06875</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
-        <v>59.83870967741935</v>
-      </c>
-      <c r="I8" t="n">
-        <v>41.0564516129032</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>38.70483870967742</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>68.36166666666668</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>47.88387096774193</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>94.46774193548387</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>78.88437499999999</v>
+        <v>68.36166666666668</v>
       </c>
     </row>
     <row r="11">
@@ -24117,13 +24191,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>33.53870967741936</v>
+        <v>50.90967741935484</v>
       </c>
     </row>
     <row r="12">
@@ -24131,13 +24205,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>38.70483870967742</v>
+        <v>101.8516129032258</v>
       </c>
     </row>
     <row r="13">
@@ -24145,13 +24219,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>50.90967741935484</v>
+        <v>78.88437499999999</v>
       </c>
     </row>
     <row r="14">
@@ -24159,10 +24233,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>63.79666666666665</v>
@@ -24179,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24199,13 +24273,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -24213,20 +24302,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>9.173548387096774</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>9.36161290322581</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.861774193548388</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11.73677419354839</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>13.70133333333334</v>
       </c>
     </row>
@@ -24235,69 +24335,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>10.16290322580645</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>10.01822580645161</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>10.6871875</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12.679</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>14.1175</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.01822580645161</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
+        <v>9.173548387096774</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.16290322580645</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>11.20064516129032</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>13.19806451612902</v>
+      </c>
+      <c r="M4" t="n">
         <v>14.09548387096774</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>13.19806451612902</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>13.19806451612902</v>
-      </c>
-      <c r="I5" t="n">
-        <v>12.679</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11.73677419354839</v>
+        <v>9.36161290322581</v>
       </c>
     </row>
     <row r="6">
@@ -24305,25 +24417,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>14.09548387096774</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
         <v>11.20064516129032</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10.6871875</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9.861774193548388</v>
       </c>
     </row>
     <row r="7">
@@ -24331,21 +24431,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>10.01822580645161</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>9.36161290322581</v>
+        <v>10.6871875</v>
       </c>
     </row>
     <row r="8">
@@ -24353,59 +24445,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>10.6871875</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10.16290322580645</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10.01822580645161</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>9.861774193548388</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>12.679</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.173548387096774</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>13.19806451612902</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>14.1175</v>
+        <v>12.679</v>
       </c>
     </row>
     <row r="11">
@@ -24413,13 +24487,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>9.36161290322581</v>
+        <v>11.73677419354839</v>
       </c>
     </row>
     <row r="12">
@@ -24427,13 +24501,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>9.861774193548388</v>
+        <v>14.09548387096774</v>
       </c>
     </row>
     <row r="13">
@@ -24441,13 +24515,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>11.73677419354839</v>
+        <v>14.1175</v>
       </c>
     </row>
     <row r="14">
@@ -24455,10 +24529,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>13.70133333333334</v>
@@ -25107,7 +25181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25127,13 +25201,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -25141,20 +25230,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>3.387096774193548</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>3.709677419354839</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.935483870967742</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.354838709677419</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>8.666666666666666</v>
       </c>
     </row>
@@ -25163,69 +25263,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>4.935483870967742</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>5.032258064516129</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.466666666666667</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>8.59375</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.032258064516129</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
+        <v>3.387096774193548</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.935483870967742</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>6.580645161290323</v>
+      </c>
+      <c r="M4" t="n">
         <v>8.548387096774194</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>6.580645161290323</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6.580645161290323</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6.466666666666667</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.354838709677419</v>
+        <v>3.709677419354839</v>
       </c>
     </row>
     <row r="6">
@@ -25233,25 +25345,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>8.548387096774194</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H6" t="n">
         <v>5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.625</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.935483870967742</v>
       </c>
     </row>
     <row r="7">
@@ -25259,21 +25359,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>5.032258064516129</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>3.709677419354839</v>
+        <v>4.625</v>
       </c>
     </row>
     <row r="8">
@@ -25281,59 +25373,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>4.625</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" t="n">
         <v>4.935483870967742</v>
       </c>
-      <c r="I8" t="n">
-        <v>5.032258064516129</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>6.466666666666667</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.387096774193548</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>6.580645161290323</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>8.59375</v>
+        <v>6.466666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -25341,13 +25415,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>3.709677419354839</v>
+        <v>6.354838709677419</v>
       </c>
     </row>
     <row r="12">
@@ -25355,13 +25429,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>4.935483870967742</v>
+        <v>8.548387096774194</v>
       </c>
     </row>
     <row r="13">
@@ -25369,13 +25443,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>6.354838709677419</v>
+        <v>8.59375</v>
       </c>
     </row>
     <row r="14">
@@ -25383,10 +25457,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>8.666666666666666</v>
@@ -25403,7 +25477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25423,16 +25497,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -25440,21 +25532,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>9.21838709677419</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>8.290967741935486</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.637333333333335</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.642258064516131</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>4.969333333333333</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.321612903225806</v>
       </c>
     </row>
@@ -25463,101 +25569,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>7.868225806451613</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>8.788709677419355</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.152096774193549</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>5.324833333333334</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>2.577833333333333</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.969333333333333</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>6.679032258064516</v>
+        <v>8.655666666666667</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>8.655666666666667</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>7.336833333333332</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>4.741833333333336</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>2.828666666666666</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.788709677419355</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.922903225806454</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H5" t="n">
-        <v>2.322333333333333</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>9.21838709677419</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.868225806451613</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>6.642258064516131</v>
-      </c>
+        <v>6.679032258064516</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>3.922903225806454</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.322333333333333</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>2.322333333333333</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.922903225806454</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.741833333333336</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.324833333333334</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.637333333333335</v>
+        <v>6.679032258064516</v>
       </c>
     </row>
     <row r="7">
@@ -25565,22 +25690,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>8.655666666666667</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>8.290967741935486</v>
+        <v>7.336833333333332</v>
       </c>
     </row>
     <row r="8">
@@ -25588,111 +25704,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>7.336833333333332</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6.679032258064516</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7.336833333333332</v>
-      </c>
-      <c r="J8" t="n">
         <v>8.152096774193549</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>4.741833333333336</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>8.788709677419355</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>8.290967741935486</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.828666666666666</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7.868225806451613</v>
-      </c>
-      <c r="I10" t="n">
-        <v>8.655666666666667</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>3.922903225806454</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>8.788709677419355</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9.21838709677419</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>4.741833333333336</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>8.152096774193549</v>
+        <v>5.324833333333334</v>
       </c>
     </row>
     <row r="13">
@@ -25700,13 +25774,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>5.324833333333334</v>
+        <v>7.637333333333335</v>
       </c>
     </row>
     <row r="14">
@@ -25714,13 +25788,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.577833333333333</v>
+        <v>2.322333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -25728,13 +25802,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>8.290967741935486</v>
+        <v>6.642258064516131</v>
       </c>
     </row>
     <row r="16">
@@ -25742,13 +25816,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>7.637333333333335</v>
+        <v>2.828666666666666</v>
       </c>
     </row>
     <row r="17">
@@ -25756,13 +25830,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>6.642258064516131</v>
+        <v>2.577833333333333</v>
       </c>
     </row>
     <row r="18">
@@ -25770,10 +25844,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>4.969333333333333</v>
@@ -25784,10 +25858,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>2.321612903225806</v>
@@ -25804,7 +25878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25833,7 +25907,37 @@
         <v>0.8</v>
       </c>
       <c r="K1" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O1" s="1" t="n">
         <v>1.2</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -25844,10 +25948,10 @@
         <v>0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="D2" t="n">
-        <v>64.39677419354837</v>
+        <v>500</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1.65</v>
@@ -25857,22 +25961,30 @@
       <c r="J2" t="n">
         <v>500</v>
       </c>
-      <c r="K2" t="n">
-        <v>16.88709677419355</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>35.79677419354838</v>
+        <v>500</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1.5</v>
@@ -25881,25 +25993,31 @@
       <c r="I3" t="n">
         <v>500</v>
       </c>
-      <c r="J3" t="n">
-        <v>18.17666666666667</v>
-      </c>
-      <c r="K3" t="n">
-        <v>12.40333333333334</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>26.61290322580645</v>
+        <v>500</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1.44</v>
@@ -25907,35 +26025,59 @@
       <c r="H4" t="n">
         <v>500</v>
       </c>
-      <c r="I4" t="n">
-        <v>21.13333333333334</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="D5" t="n">
-        <v>23.75</v>
+        <v>500</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H5" t="n">
-        <v>31.26666666666667</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>37.8967741935484</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.01333333333333</v>
+      </c>
+      <c r="R5" t="n">
         <v>9.517741935483867</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>12.40333333333334</v>
+      </c>
+      <c r="U5" t="n">
+        <v>16.88709677419355</v>
       </c>
     </row>
     <row r="6">
@@ -25943,169 +26085,231 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="D6" t="n">
-        <v>31.26666666666667</v>
+        <v>500</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16.38666666666667</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13.85333333333334</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13.01333333333333</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>500</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.4</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>64.39677419354837</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.26</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>37.8967741935484</v>
-      </c>
+      <c r="J7" t="n">
+        <v>500</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="C8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35.79677419354838</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="D8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>500</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>26.61290322580645</v>
-      </c>
-      <c r="I8" t="n">
-        <v>29.075</v>
-      </c>
-      <c r="J8" t="n">
-        <v>27.8016129032258</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.99</v>
       </c>
       <c r="D9" t="n">
         <v>56.47000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>45.01935483870968</v>
       </c>
-      <c r="K9" t="n">
-        <v>500</v>
-      </c>
+      <c r="N9" t="n">
+        <v>27.8016129032258</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>13.85333333333334</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>18.17666666666667</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>45.01935483870968</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>56.47000000000001</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>29.075</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>35.79677419354838</v>
-      </c>
-      <c r="I10" t="n">
-        <v>56.47000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>500</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>16.38666666666667</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>21.13333333333334</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C11" t="n">
-        <v>1.32</v>
+        <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>16.38666666666667</v>
+        <v>26.61290322580645</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>64.39677419354837</v>
       </c>
-      <c r="I11" t="n">
-        <v>500</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>35.79677419354838</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>26.61290322580645</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>31.26666666666667</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.6</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D12" t="n">
-        <v>21.13333333333334</v>
+        <v>29.075</v>
       </c>
     </row>
     <row r="13">
@@ -26113,13 +26317,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D13" t="n">
-        <v>500</v>
+        <v>27.8016129032258</v>
       </c>
     </row>
     <row r="14">
@@ -26127,10 +26331,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="D14" t="n">
         <v>500</v>
@@ -26141,13 +26345,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8</v>
+        <v>1.26</v>
       </c>
       <c r="C15" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>45.01935483870968</v>
+        <v>37.8967741935484</v>
       </c>
     </row>
     <row r="16">
@@ -26155,13 +26359,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C16" t="n">
-        <v>1.11</v>
+        <v>0.4</v>
       </c>
       <c r="D16" t="n">
-        <v>27.8016129032258</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="17">
@@ -26169,13 +26373,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C17" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D17" t="n">
-        <v>13.85333333333334</v>
+        <v>16.38666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -26183,13 +26387,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.8</v>
       </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="D18" t="n">
-        <v>18.17666666666667</v>
+        <v>13.85333333333334</v>
       </c>
     </row>
     <row r="19">
@@ -26197,13 +26401,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C19" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>500</v>
+        <v>13.01333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -26211,13 +26415,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="C20" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="D20" t="n">
-        <v>500</v>
+        <v>31.26666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -26225,13 +26429,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C21" t="n">
         <v>1.2</v>
       </c>
-      <c r="C21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D21" t="n">
-        <v>37.8967741935484</v>
+        <v>9.517741935483867</v>
       </c>
     </row>
     <row r="22">
@@ -26239,13 +26443,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C22" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D22" t="n">
-        <v>13.01333333333333</v>
+        <v>21.13333333333334</v>
       </c>
     </row>
     <row r="23">
@@ -26253,13 +26457,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C23" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D23" t="n">
-        <v>9.517741935483867</v>
+        <v>18.17666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -26267,10 +26471,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C24" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.5</v>
       </c>
       <c r="D24" t="n">
         <v>12.40333333333334</v>
@@ -26281,10 +26485,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.65</v>
       </c>
       <c r="D25" t="n">
         <v>16.88709677419355</v>
@@ -26301,7 +26505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26321,16 +26525,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -26338,21 +26560,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>25.59032258064516</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>11.21612903225806</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13.18333333333334</v>
+      </c>
+      <c r="N2" t="n">
+        <v>16.09193548387097</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>17.35333333333334</v>
+      </c>
+      <c r="Q2" t="n">
         <v>25.23548387096774</v>
       </c>
     </row>
@@ -26361,101 +26597,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>37.63548387096775</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>15.35483870967742</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18.8758064516129</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>30.03500000000001</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>40.23666666666666</v>
       </c>
-      <c r="K3" t="n">
-        <v>17.35333333333334</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>43.77258064516131</v>
+        <v>22.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>27.61333333333334</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>41.32000000000001</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>46.86833333333335</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.35483870967742</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>61.82580645161288</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H5" t="n">
-        <v>68.25000000000001</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>25.59032258064516</v>
+      </c>
+      <c r="I5" t="n">
+        <v>37.63548387096775</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>16.09193548387097</v>
-      </c>
+        <v>43.77258064516131</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>61.82580645161288</v>
+      </c>
+      <c r="N5" t="n">
+        <v>68.25000000000001</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>68.25000000000001</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61.82580645161288</v>
-      </c>
-      <c r="I6" t="n">
-        <v>41.32000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30.03500000000001</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13.18333333333334</v>
+        <v>43.77258064516131</v>
       </c>
     </row>
     <row r="7">
@@ -26463,22 +26718,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>11.21612903225806</v>
+        <v>27.61333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -26486,111 +26732,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>27.61333333333334</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>43.77258064516131</v>
-      </c>
-      <c r="I8" t="n">
-        <v>27.61333333333334</v>
-      </c>
-      <c r="J8" t="n">
         <v>18.8758064516129</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>41.32000000000001</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>15.35483870967742</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>11.21612903225806</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>46.86833333333335</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>37.63548387096775</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>61.82580645161288</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>15.35483870967742</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>25.59032258064516</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>41.32000000000001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>18.8758064516129</v>
+        <v>30.03500000000001</v>
       </c>
     </row>
     <row r="13">
@@ -26598,13 +26802,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>30.03500000000001</v>
+        <v>13.18333333333334</v>
       </c>
     </row>
     <row r="14">
@@ -26612,13 +26816,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>40.23666666666666</v>
+        <v>68.25000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -26626,13 +26830,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>11.21612903225806</v>
+        <v>16.09193548387097</v>
       </c>
     </row>
     <row r="16">
@@ -26640,13 +26844,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>13.18333333333334</v>
+        <v>46.86833333333335</v>
       </c>
     </row>
     <row r="17">
@@ -26654,13 +26858,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>16.09193548387097</v>
+        <v>40.23666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -26668,10 +26872,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>17.35333333333334</v>
@@ -26682,10 +26886,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>25.23548387096774</v>
@@ -26702,7 +26906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26722,16 +26926,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -26739,21 +26961,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>4.977419354838709</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>1.490322580645161</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.173333333333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.270967741935484</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>1.700000000000001</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.693548387096775</v>
       </c>
     </row>
@@ -26762,101 +26998,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>3.15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>2.351612903225806</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.945161290322582</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1.561666666666667</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>1.653333333333333</v>
       </c>
-      <c r="K3" t="n">
-        <v>1.700000000000001</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.796774193548387</v>
+        <v>3.58</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>2.931666666666667</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>2.059999999999999</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>2.169999999999999</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.351612903225806</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.37258064516129</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H5" t="n">
-        <v>2.556666666666667</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>4.977419354838709</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.15</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>1.270967741935484</v>
-      </c>
+        <v>2.796774193548387</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>2.37258064516129</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.556666666666667</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>2.556666666666667</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.37258064516129</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.059999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.561666666666667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.173333333333333</v>
+        <v>2.796774193548387</v>
       </c>
     </row>
     <row r="7">
@@ -26864,22 +27119,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>1.490322580645161</v>
+        <v>2.931666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -26887,111 +27133,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2.931666666666667</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.796774193548387</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.931666666666667</v>
-      </c>
-      <c r="J8" t="n">
         <v>1.945161290322582</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>2.059999999999999</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>2.351612903225806</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>1.490322580645161</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.169999999999999</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>2.37258064516129</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.351612903225806</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.977419354838709</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>2.059999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>1.945161290322582</v>
+        <v>1.561666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -26999,13 +27203,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.561666666666667</v>
+        <v>1.173333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -27013,13 +27217,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.653333333333333</v>
+        <v>2.556666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -27027,13 +27231,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>1.490322580645161</v>
+        <v>1.270967741935484</v>
       </c>
     </row>
     <row r="16">
@@ -27041,13 +27245,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.173333333333333</v>
+        <v>2.169999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -27055,13 +27259,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>1.270967741935484</v>
+        <v>1.653333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -27069,10 +27273,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>1.700000000000001</v>
@@ -27083,10 +27287,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>1.693548387096775</v>
@@ -27103,7 +27307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27123,16 +27327,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -27140,21 +27362,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>30.56774193548387</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>12.70645161290322</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.35666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17.36290322580645</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>19.05333333333333</v>
+      </c>
+      <c r="Q2" t="n">
         <v>26.92903225806451</v>
       </c>
     </row>
@@ -27163,101 +27399,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>40.78548387096773</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>17.70645161290322</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.82096774193548</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>31.59666666666667</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>41.89000000000001</v>
       </c>
-      <c r="K3" t="n">
-        <v>19.05333333333333</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>46.56935483870967</v>
+        <v>26.21999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>26.21999999999999</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>30.54500000000001</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>43.37999999999999</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>49.03833333333333</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17.70645161290322</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>64.19838709677421</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H5" t="n">
-        <v>70.80666666666667</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>30.56774193548387</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40.78548387096773</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>17.36290322580645</v>
-      </c>
+        <v>46.56935483870967</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>64.19838709677421</v>
+      </c>
+      <c r="N5" t="n">
+        <v>70.80666666666667</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>70.80666666666667</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>64.19838709677421</v>
-      </c>
-      <c r="I6" t="n">
-        <v>43.37999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31.59666666666667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>14.35666666666666</v>
+        <v>46.56935483870967</v>
       </c>
     </row>
     <row r="7">
@@ -27265,22 +27520,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>26.21999999999999</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>12.70645161290322</v>
+        <v>30.54500000000001</v>
       </c>
     </row>
     <row r="8">
@@ -27288,111 +27534,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54500000000001</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>46.56935483870967</v>
-      </c>
-      <c r="I8" t="n">
-        <v>30.54500000000001</v>
-      </c>
-      <c r="J8" t="n">
         <v>20.82096774193548</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>43.37999999999999</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>17.70645161290322</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>12.70645161290322</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>49.03833333333333</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>40.78548387096773</v>
-      </c>
-      <c r="I10" t="n">
-        <v>26.21999999999999</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>64.19838709677421</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>17.70645161290322</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>30.56774193548387</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>43.37999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>20.82096774193548</v>
+        <v>31.59666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -27400,13 +27604,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>31.59666666666667</v>
+        <v>14.35666666666666</v>
       </c>
     </row>
     <row r="14">
@@ -27414,13 +27618,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>41.89000000000001</v>
+        <v>70.80666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -27428,13 +27632,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>12.70645161290322</v>
+        <v>17.36290322580645</v>
       </c>
     </row>
     <row r="16">
@@ -27442,13 +27646,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>14.35666666666666</v>
+        <v>49.03833333333333</v>
       </c>
     </row>
     <row r="17">
@@ -27456,13 +27660,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>17.36290322580645</v>
+        <v>41.89000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -27470,10 +27674,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>19.05333333333333</v>
@@ -27484,10 +27688,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>26.92903225806451</v>
@@ -27504,7 +27708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27524,16 +27728,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -27541,21 +27763,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>9.226774193548387</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>9.851290322580647</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10.33566666666667</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11.05967741935483</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>12.28833333333333</v>
+      </c>
+      <c r="Q2" t="n">
         <v>14.31193548387097</v>
       </c>
     </row>
@@ -27564,101 +27800,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>10.22241935483871</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>9.43064516129032</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.904193548387106</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>11.97716666666667</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>14.05483333333334</v>
       </c>
-      <c r="K3" t="n">
-        <v>12.28833333333333</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>11.10774193548387</v>
+        <v>9.630333333333333</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>9.630333333333333</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>12.57116666666666</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>14.06399999999999</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.43064516129032</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13.19516129032258</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H5" t="n">
-        <v>14.45733333333333</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>9.226774193548387</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.22241935483871</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>11.05967741935483</v>
-      </c>
+        <v>11.10774193548387</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>13.19516129032258</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14.45733333333333</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>14.45733333333333</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>13.19516129032258</v>
-      </c>
-      <c r="I6" t="n">
-        <v>12.57116666666666</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11.97716666666667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10.33566666666667</v>
+        <v>11.10774193548387</v>
       </c>
     </row>
     <row r="7">
@@ -27666,22 +27921,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>9.630333333333333</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>9.851290322580647</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="8">
@@ -27689,111 +27935,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>11.10774193548387</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="J8" t="n">
         <v>9.904193548387106</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>12.57116666666666</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>9.43064516129032</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>9.851290322580647</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>14.06399999999999</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10.22241935483871</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.630333333333333</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>13.19516129032258</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>9.43064516129032</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9.226774193548387</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>12.57116666666666</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>9.904193548387106</v>
+        <v>11.97716666666667</v>
       </c>
     </row>
     <row r="13">
@@ -27801,13 +28005,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>11.97716666666667</v>
+        <v>10.33566666666667</v>
       </c>
     </row>
     <row r="14">
@@ -27815,13 +28019,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>14.05483333333334</v>
+        <v>14.45733333333333</v>
       </c>
     </row>
     <row r="15">
@@ -27829,13 +28033,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>9.851290322580647</v>
+        <v>11.05967741935483</v>
       </c>
     </row>
     <row r="16">
@@ -27843,13 +28047,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>10.33566666666667</v>
+        <v>14.06399999999999</v>
       </c>
     </row>
     <row r="17">
@@ -27857,13 +28061,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>11.05967741935483</v>
+        <v>14.05483333333334</v>
       </c>
     </row>
     <row r="18">
@@ -27871,10 +28075,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>12.28833333333333</v>
@@ -27885,10 +28089,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>14.31193548387097</v>
@@ -27905,7 +28109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27925,16 +28129,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -27942,21 +28164,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>2.645161290322581</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>6.066666666666666</v>
+      </c>
+      <c r="Q2" t="n">
         <v>9.838709677419354</v>
       </c>
     </row>
@@ -27965,101 +28201,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>4.354838709677419</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.870967741935484</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>9</v>
       </c>
-      <c r="K3" t="n">
-        <v>6.066666666666666</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3.633333333333333</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>3.633333333333333</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>3.766666666666667</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>8.65</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7.016129032258065</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H5" t="n">
-        <v>8.766666666666667</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>2.645161290322581</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.354838709677419</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>7.016129032258065</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8.766666666666667</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>8.766666666666667</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7.016129032258065</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -28067,22 +28322,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>3.633333333333333</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>5</v>
+        <v>3.766666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -28090,111 +28336,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>3.766666666666667</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.766666666666667</v>
-      </c>
-      <c r="J8" t="n">
         <v>3.870967741935484</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.354838709677419</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.633333333333333</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>7.016129032258065</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.645161290322581</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>6.45</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>3.870967741935484</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -28202,10 +28406,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -28216,13 +28420,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8.766666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -28230,13 +28434,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -28244,13 +28448,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="17">
@@ -28258,13 +28462,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -28272,10 +28476,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>6.066666666666666</v>
@@ -28286,10 +28490,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>9.838709677419354</v>
@@ -39560,7 +39764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39586,7 +39790,31 @@
         <v>0.76</v>
       </c>
       <c r="J1" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L1" s="1" t="n">
         <v>1.03</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -39597,204 +39825,254 @@
         <v>0.51</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="D2" t="n">
-        <v>79.33998623537506</v>
+        <v>750</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.9</v>
+        <v>0.51</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>750</v>
       </c>
-      <c r="J2" t="n">
-        <v>28.71403571495777</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>49.13314069793289</v>
+        <v>750</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="n">
         <v>750</v>
       </c>
-      <c r="I3" t="n">
-        <v>38.96997069057129</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>39.83499272849312</v>
+        <v>750</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H4" t="n">
-        <v>46.24586217273549</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>104.4608186819114</v>
+      </c>
+      <c r="N4" t="n">
+        <v>56.09510453850078</v>
+      </c>
+      <c r="O4" t="n">
+        <v>27.58086167220658</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>28.71403571495777</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.51</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.32</v>
-      </c>
       <c r="D5" t="n">
-        <v>40.28187386569873</v>
+        <v>79.33998623537506</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H5" t="n">
-        <v>40.28187386569873</v>
-      </c>
-      <c r="I5" t="n">
-        <v>34.64110157848134</v>
-      </c>
-      <c r="J5" t="n">
-        <v>27.58086167220658</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>750</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>46.24586217273549</v>
+        <v>49.13314069793289</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>39.83499272849312</v>
-      </c>
+        <v>1.03</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>38.90992835209825</v>
-      </c>
-      <c r="J6" t="n">
-        <v>56.09510453850078</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.51</v>
+        <v>0.99</v>
       </c>
       <c r="C7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D7" t="n">
+        <v>51.57648061354919</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>1.44</v>
-      </c>
-      <c r="D7" t="n">
-        <v>750</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.41</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>104.4608186819114</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>51.57648061354919</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>38.90992835209825</v>
+      </c>
+      <c r="O7" t="n">
+        <v>34.64110157848134</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>38.96997069057129</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="D8" t="n">
         <v>750</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>79.33998623537506</v>
+      </c>
+      <c r="K8" t="n">
         <v>49.13314069793289</v>
       </c>
-      <c r="I8" t="n">
-        <v>51.57648061354919</v>
-      </c>
-      <c r="J8" t="n">
-        <v>750</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>39.83499272849312</v>
+      </c>
+      <c r="O8" t="n">
+        <v>40.28187386569873</v>
+      </c>
+      <c r="P8" t="n">
+        <v>46.24586217273549</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="D9" t="n">
-        <v>51.57648061354919</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>79.33998623537506</v>
-      </c>
-      <c r="I9" t="n">
-        <v>750</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>104.4608186819114</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C10" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D10" t="n">
-        <v>38.90992835209825</v>
+        <v>39.83499272849312</v>
       </c>
     </row>
     <row r="11">
@@ -39802,13 +40080,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.32</v>
-      </c>
       <c r="D11" t="n">
-        <v>34.64110157848134</v>
+        <v>38.90992835209825</v>
       </c>
     </row>
     <row r="12">
@@ -39816,13 +40094,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="D12" t="n">
-        <v>38.96997069057129</v>
+        <v>56.09510453850078</v>
       </c>
     </row>
     <row r="13">
@@ -39830,13 +40108,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="D13" t="n">
-        <v>750</v>
+        <v>40.28187386569873</v>
       </c>
     </row>
     <row r="14">
@@ -39844,13 +40122,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="C14" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="D14" t="n">
-        <v>750</v>
+        <v>34.64110157848134</v>
       </c>
     </row>
     <row r="15">
@@ -39858,13 +40136,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.03</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D15" t="n">
-        <v>104.4608186819114</v>
+        <v>27.58086167220658</v>
       </c>
     </row>
     <row r="16">
@@ -39872,13 +40150,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C16" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D16" t="n">
-        <v>56.09510453850078</v>
+        <v>46.24586217273549</v>
       </c>
     </row>
     <row r="17">
@@ -39886,13 +40164,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C17" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D17" t="n">
-        <v>27.58086167220658</v>
+        <v>38.96997069057129</v>
       </c>
     </row>
     <row r="18">
@@ -39900,10 +40178,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>28.71403571495777</v>
@@ -39920,7 +40198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39940,13 +40218,28 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="2">
@@ -39954,20 +40247,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>150.7897040605643</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.9</v>
+        <v>0.51</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>103.454131161687</v>
+      </c>
+      <c r="K2" t="n">
+        <v>112.8874681285059</v>
+      </c>
+      <c r="L2" t="n">
+        <v>124.0850166197903</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>132.8922153435071</v>
       </c>
     </row>
@@ -39976,69 +40280,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>169.0486774838852</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
+        <v>117.7084012130629</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>131.7875127942681</v>
+      </c>
+      <c r="L3" t="n">
+        <v>154.0344701248741</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>159.6535488404779</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.51</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="D4" t="n">
+        <v>117.7084012130629</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H4" t="n">
+        <v>150.7897040605643</v>
+      </c>
+      <c r="I4" t="n">
+        <v>169.0486774838852</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>187.0799865756796</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>204.2907781306715</v>
+      </c>
+      <c r="M4" t="n">
         <v>206.2418084296614</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.51</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="D5" t="n">
-        <v>204.2907781306715</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H5" t="n">
-        <v>204.2907781306715</v>
-      </c>
-      <c r="I5" t="n">
-        <v>154.0344701248741</v>
-      </c>
-      <c r="J5" t="n">
-        <v>124.0850166197903</v>
+        <v>103.454131161687</v>
       </c>
     </row>
     <row r="6">
@@ -40046,25 +40362,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.51</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>206.2418084296614</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
         <v>187.0799865756796</v>
-      </c>
-      <c r="I6" t="n">
-        <v>131.7875127942681</v>
-      </c>
-      <c r="J6" t="n">
-        <v>112.8874681285059</v>
       </c>
     </row>
     <row r="7">
@@ -40072,21 +40376,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>117.7084012130629</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>103.454131161687</v>
+        <v>131.7875127942681</v>
       </c>
     </row>
     <row r="8">
@@ -40094,59 +40390,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>131.7875127942681</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H8" t="n">
-        <v>169.0486774838852</v>
-      </c>
-      <c r="I8" t="n">
-        <v>117.7084012130629</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>112.8874681285059</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>0.51</v>
       </c>
       <c r="D9" t="n">
-        <v>154.0344701248741</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>150.7897040605643</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>204.2907781306715</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.76</v>
       </c>
-      <c r="C10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D10" t="n">
-        <v>159.6535488404779</v>
+        <v>154.0344701248741</v>
       </c>
     </row>
     <row r="11">
@@ -40154,13 +40432,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.03</v>
       </c>
-      <c r="C11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="D11" t="n">
-        <v>103.454131161687</v>
+        <v>124.0850166197903</v>
       </c>
     </row>
     <row r="12">
@@ -40168,13 +40446,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>112.8874681285059</v>
+        <v>206.2418084296614</v>
       </c>
     </row>
     <row r="13">
@@ -40182,13 +40460,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>124.0850166197903</v>
+        <v>159.6535488404779</v>
       </c>
     </row>
     <row r="14">
@@ -40196,10 +40474,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="n">
         <v>1.03</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.5</v>
       </c>
       <c r="D14" t="n">
         <v>132.8922153435071</v>
@@ -40216,7 +40494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40245,7 +40523,37 @@
         <v>0.8</v>
       </c>
       <c r="K1" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O1" s="1" t="n">
         <v>1.2</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -40256,98 +40564,136 @@
         <v>0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="D2" t="n">
-        <v>122.9820934753442</v>
+        <v>750</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>750</v>
       </c>
-      <c r="K2" t="n">
-        <v>20.34221024817367</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>61.33424223442277</v>
+        <v>750</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>750</v>
       </c>
-      <c r="J3" t="n">
-        <v>22.20015741905133</v>
-      </c>
-      <c r="K3" t="n">
-        <v>17.40882059386177</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>41.81214100687014</v>
+        <v>750</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="n">
         <v>750</v>
       </c>
-      <c r="I4" t="n">
-        <v>26.16758997688668</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="D5" t="n">
-        <v>31.29191144524832</v>
+        <v>750</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H5" t="n">
-        <v>37.66530437420806</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>67.09223818467945</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>21.91179405308322</v>
+      </c>
+      <c r="R5" t="n">
         <v>14.91524186119661</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>17.40882059386177</v>
+      </c>
+      <c r="U5" t="n">
+        <v>20.34221024817367</v>
       </c>
     </row>
     <row r="6">
@@ -40355,89 +40701,109 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="D6" t="n">
-        <v>37.66530437420806</v>
+        <v>750</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H6" t="n">
-        <v>31.29191144524832</v>
-      </c>
-      <c r="I6" t="n">
-        <v>22.67783370408718</v>
-      </c>
-      <c r="J6" t="n">
-        <v>19.88495603449193</v>
-      </c>
-      <c r="K6" t="n">
-        <v>21.91179405308322</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>750</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.4</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>122.9820934753442</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>67.09223818467945</v>
-      </c>
+      <c r="J7" t="n">
+        <v>750</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D8" t="n">
+        <v>61.33424223442277</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>750</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H8" t="n">
-        <v>41.81214100687014</v>
-      </c>
-      <c r="I8" t="n">
-        <v>47.87963990778125</v>
-      </c>
-      <c r="J8" t="n">
-        <v>48.68781149177096</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.99</v>
       </c>
       <c r="D9" t="n">
         <v>102.9277941295601</v>
@@ -40447,77 +40813,119 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>82.9507330603619</v>
       </c>
-      <c r="K9" t="n">
-        <v>750</v>
-      </c>
+      <c r="N9" t="n">
+        <v>48.68781149177096</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>19.88495603449193</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>22.20015741905133</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="C10" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>47.87963990778125</v>
+        <v>82.9507330603619</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H10" t="n">
-        <v>61.33424223442277</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
         <v>102.9277941295601</v>
       </c>
-      <c r="J10" t="n">
-        <v>750</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>47.87963990778125</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>22.67783370408718</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>26.16758997688668</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C11" t="n">
-        <v>1.32</v>
+        <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>22.67783370408718</v>
+        <v>41.81214100687014</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>122.9820934753442</v>
       </c>
-      <c r="I11" t="n">
-        <v>750</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>61.33424223442277</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>41.81214100687014</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>31.29191144524832</v>
+      </c>
+      <c r="R11" t="n">
+        <v>37.66530437420806</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.6</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D12" t="n">
-        <v>26.16758997688668</v>
+        <v>47.87963990778125</v>
       </c>
     </row>
     <row r="13">
@@ -40525,13 +40933,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D13" t="n">
-        <v>750</v>
+        <v>48.68781149177096</v>
       </c>
     </row>
     <row r="14">
@@ -40539,10 +40947,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="D14" t="n">
         <v>750</v>
@@ -40553,13 +40961,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8</v>
+        <v>1.26</v>
       </c>
       <c r="C15" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>82.9507330603619</v>
+        <v>67.09223818467945</v>
       </c>
     </row>
     <row r="16">
@@ -40567,13 +40975,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C16" t="n">
-        <v>1.11</v>
+        <v>0.4</v>
       </c>
       <c r="D16" t="n">
-        <v>48.68781149177096</v>
+        <v>31.29191144524832</v>
       </c>
     </row>
     <row r="17">
@@ -40581,13 +40989,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C17" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D17" t="n">
-        <v>19.88495603449193</v>
+        <v>22.67783370408718</v>
       </c>
     </row>
     <row r="18">
@@ -40595,13 +41003,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.8</v>
       </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="D18" t="n">
-        <v>22.20015741905133</v>
+        <v>19.88495603449193</v>
       </c>
     </row>
     <row r="19">
@@ -40609,13 +41017,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C19" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>750</v>
+        <v>21.91179405308322</v>
       </c>
     </row>
     <row r="20">
@@ -40623,13 +41031,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="C20" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="D20" t="n">
-        <v>750</v>
+        <v>37.66530437420806</v>
       </c>
     </row>
     <row r="21">
@@ -40637,13 +41045,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C21" t="n">
         <v>1.2</v>
       </c>
-      <c r="C21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D21" t="n">
-        <v>67.09223818467945</v>
+        <v>14.91524186119661</v>
       </c>
     </row>
     <row r="22">
@@ -40651,13 +41059,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C22" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D22" t="n">
-        <v>21.91179405308322</v>
+        <v>26.16758997688668</v>
       </c>
     </row>
     <row r="23">
@@ -40665,13 +41073,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C23" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D23" t="n">
-        <v>14.91524186119661</v>
+        <v>22.20015741905133</v>
       </c>
     </row>
     <row r="24">
@@ -40679,10 +41087,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C24" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.5</v>
       </c>
       <c r="D24" t="n">
         <v>17.40882059386177</v>
@@ -40693,10 +41101,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.65</v>
       </c>
       <c r="D25" t="n">
         <v>20.34221024817367</v>
@@ -40713,7 +41121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40733,16 +41141,34 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="2">
@@ -40750,21 +41176,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
       </c>
       <c r="D2" t="n">
         <v>95.73813761191575</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>36.89250723386974</v>
+      </c>
+      <c r="M2" t="n">
+        <v>39.64485631610457</v>
+      </c>
+      <c r="N2" t="n">
+        <v>44.62339077489946</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>43.85768942859519</v>
+      </c>
+      <c r="Q2" t="n">
         <v>53.19952334075953</v>
       </c>
     </row>
@@ -40773,101 +41213,120 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>114.6063230037952</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>53.50524369303921</v>
+      </c>
+      <c r="K3" t="n">
+        <v>59.79915136146226</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>74.37987900181817</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>83.90657993540394</v>
       </c>
-      <c r="K3" t="n">
-        <v>43.85768942859519</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>119.9925329428989</v>
+        <v>78.37750114762505</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>78.37750114762505</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>82.49262616035813</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>98.45648853396753</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>99.580722383241</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4</v>
+        <v>1.05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.32</v>
+        <v>0.8</v>
       </c>
       <c r="D5" t="n">
-        <v>138.7191578987137</v>
+        <v>53.50524369303921</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>139.8871736298253</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>95.73813761191575</v>
+      </c>
+      <c r="I5" t="n">
+        <v>114.6063230037952</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>44.62339077489946</v>
-      </c>
+        <v>119.9925329428989</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>138.7191578987137</v>
+      </c>
+      <c r="N5" t="n">
+        <v>139.8871736298253</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="D6" t="n">
-        <v>139.8871736298253</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="H6" t="n">
-        <v>138.7191578987137</v>
-      </c>
-      <c r="I6" t="n">
-        <v>98.45648853396753</v>
-      </c>
-      <c r="J6" t="n">
-        <v>74.37987900181817</v>
-      </c>
-      <c r="K6" t="n">
-        <v>39.64485631610457</v>
+        <v>119.9925329428989</v>
       </c>
     </row>
     <row r="7">
@@ -40875,22 +41334,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.99</v>
-      </c>
       <c r="D7" t="n">
-        <v>78.37750114762505</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>36.89250723386974</v>
+        <v>82.49262616035813</v>
       </c>
     </row>
     <row r="8">
@@ -40898,111 +41348,69 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="n">
-        <v>82.49262616035813</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H8" t="n">
-        <v>119.9925329428989</v>
-      </c>
-      <c r="I8" t="n">
-        <v>82.49262616035813</v>
-      </c>
-      <c r="J8" t="n">
         <v>59.79915136146226</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>98.45648853396753</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>53.50524369303921</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>36.89250723386974</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>99.580722383241</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>114.6063230037952</v>
-      </c>
-      <c r="I10" t="n">
-        <v>78.37750114762505</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>138.7191578987137</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>53.50524369303921</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H11" t="n">
-        <v>95.73813761191575</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>98.45648853396753</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.8</v>
       </c>
-      <c r="C12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="D12" t="n">
-        <v>59.79915136146226</v>
+        <v>74.37987900181817</v>
       </c>
     </row>
     <row r="13">
@@ -41010,13 +41418,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>74.37987900181817</v>
+        <v>39.64485631610457</v>
       </c>
     </row>
     <row r="14">
@@ -41024,13 +41432,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>83.90657993540394</v>
+        <v>139.8871736298253</v>
       </c>
     </row>
     <row r="15">
@@ -41038,13 +41446,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="D15" t="n">
-        <v>36.89250723386974</v>
+        <v>44.62339077489946</v>
       </c>
     </row>
     <row r="16">
@@ -41052,13 +41460,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>39.64485631610457</v>
+        <v>99.580722383241</v>
       </c>
     </row>
     <row r="17">
@@ -41066,13 +41474,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>44.62339077489946</v>
+        <v>83.90657993540394</v>
       </c>
     </row>
     <row r="18">
@@ -41080,10 +41488,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.5</v>
       </c>
       <c r="D18" t="n">
         <v>43.85768942859519</v>
@@ -41094,10 +41502,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.65</v>
       </c>
       <c r="D19" t="n">
         <v>53.19952334075953</v>

--- a/excel_results/source.xlsx
+++ b/excel_results/source.xlsx
@@ -22931,7 +22931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22992,7 +22992,7 @@
         <v>0.51</v>
       </c>
       <c r="C2" t="n">
-        <v>1.44</v>
+        <v>0.51</v>
       </c>
       <c r="D2" t="n">
         <v>500</v>
@@ -23001,14 +23001,14 @@
         <v>1.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>500</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>500</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -23022,7 +23022,7 @@
         <v>0.76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="D3" t="n">
         <v>500</v>
@@ -23030,14 +23030,14 @@
       <c r="G3" s="1" t="n">
         <v>1.44</v>
       </c>
-      <c r="H3" t="n">
-        <v>500</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>500</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -23049,13 +23049,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="D4" t="n">
-        <v>500</v>
+        <v>41.31935483870968</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1.03</v>
@@ -23064,7 +23064,9 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>500</v>
+      </c>
       <c r="M4" t="n">
         <v>55.53870967741936</v>
       </c>
@@ -23088,10 +23090,10 @@
         <v>0.9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>41.31935483870968</v>
+        <v>500</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>0.99</v>
@@ -23099,10 +23101,10 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
         <v>500</v>
       </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -23127,10 +23129,10 @@
         <v>0.9</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
         <v>500</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -23157,7 +23159,9 @@
         <v>0.76</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>500</v>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>29.5032258064516</v>
@@ -23174,14 +23178,16 @@
       <c r="Q7" t="n">
         <v>31.57812500000001</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="C8" t="n">
         <v>0.99</v>
@@ -23192,7 +23198,9 @@
       <c r="G8" s="1" t="n">
         <v>0.51</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>500</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>41.31935483870968</v>
@@ -23211,7 +23219,9 @@
       <c r="P8" t="n">
         <v>37.45483870967742</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>500</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -23219,13 +23229,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="C9" t="n">
         <v>1.03</v>
       </c>
       <c r="D9" t="n">
-        <v>55.53870967741936</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -23233,13 +23243,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.51</v>
+        <v>1.03</v>
       </c>
       <c r="D10" t="n">
-        <v>25.5258064516129</v>
+        <v>55.53870967741936</v>
       </c>
     </row>
     <row r="11">
@@ -23247,13 +23257,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.76</v>
+        <v>1.44</v>
       </c>
       <c r="D11" t="n">
-        <v>23.759375</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
@@ -23264,10 +23274,10 @@
         <v>1.11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.03</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>31.54193548387097</v>
+        <v>25.5258064516129</v>
       </c>
     </row>
     <row r="13">
@@ -23275,13 +23285,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>30.54838709677419</v>
+        <v>23.759375</v>
       </c>
     </row>
     <row r="14">
@@ -23289,13 +23299,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="D14" t="n">
-        <v>25.21333333333332</v>
+        <v>31.54193548387097</v>
       </c>
     </row>
     <row r="15">
@@ -23303,13 +23313,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="C15" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="n">
-        <v>18.55806451612903</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
@@ -23317,13 +23327,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="C16" t="n">
         <v>0.51</v>
       </c>
       <c r="D16" t="n">
-        <v>37.45483870967742</v>
+        <v>30.54838709677419</v>
       </c>
     </row>
     <row r="17">
@@ -23331,13 +23341,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="C17" t="n">
         <v>0.76</v>
       </c>
       <c r="D17" t="n">
-        <v>31.57812500000001</v>
+        <v>25.21333333333332</v>
       </c>
     </row>
     <row r="18">
@@ -23345,12 +23355,82 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="C18" t="n">
         <v>1.03</v>
       </c>
       <c r="D18" t="n">
+        <v>18.55806451612903</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D19" t="n">
+        <v>37.45483870967742</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D20" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31.57812500000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D22" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D23" t="n">
         <v>22.60666666666667</v>
       </c>
     </row>
@@ -25878,7 +25958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25898,45 +25978,33 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R1" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S1" s="1" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T1" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U1" s="1" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -25945,16 +26013,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D2" t="n">
-        <v>500</v>
+        <v>64.39677419354837</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -25962,300 +26030,209 @@
         <v>500</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>37.8967741935484</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13.01333333333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.517741935483867</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>12.40333333333334</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>16.88709677419355</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9</v>
       </c>
       <c r="D3" t="n">
         <v>500</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>500</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>45.01935483870968</v>
+      </c>
+      <c r="K3" t="n">
+        <v>27.8016129032258</v>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>13.85333333333334</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>18.17666666666667</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35.79677419354838</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>500</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>1.44</v>
       </c>
       <c r="H4" t="n">
         <v>500</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>56.47000000000001</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>29.075</v>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>16.38666666666667</v>
+      </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>21.13333333333334</v>
+      </c>
+      <c r="P4" t="n">
+        <v>500</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="C5" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="D5" t="n">
+        <v>56.47000000000001</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>64.39677419354837</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.79677419354838</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>26.61290322580645</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>31.26666666666667</v>
+      </c>
+      <c r="O5" t="n">
         <v>500</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>37.8967741935484</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13.01333333333333</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9.517741935483867</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>12.40333333333334</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16.88709677419355</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.65</v>
       </c>
       <c r="D6" t="n">
         <v>500</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>500</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
-        <v>64.39677419354837</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>500</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>45.01935483870968</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79677419354838</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
         <v>500</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D9" t="n">
-        <v>56.47000000000001</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>45.01935483870968</v>
-      </c>
-      <c r="N9" t="n">
-        <v>27.8016129032258</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>13.85333333333334</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>18.17666666666667</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>26.61290322580645</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>45.01935483870968</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>56.47000000000001</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
         <v>29.075</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>16.38666666666667</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>21.13333333333334</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -26265,51 +26242,24 @@
         <v>1.11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D11" t="n">
-        <v>26.61290322580645</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>64.39677419354837</v>
-      </c>
-      <c r="L11" t="n">
-        <v>35.79677419354838</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>26.61290322580645</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>31.26666666666667</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+        <v>27.8016129032258</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D12" t="n">
-        <v>29.075</v>
+        <v>37.8967741935484</v>
       </c>
     </row>
     <row r="13">
@@ -26317,13 +26267,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D13" t="n">
-        <v>27.8016129032258</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="14">
@@ -26331,13 +26281,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="C14" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D14" t="n">
-        <v>500</v>
+        <v>16.38666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -26345,13 +26295,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D15" t="n">
-        <v>37.8967741935484</v>
+        <v>13.85333333333334</v>
       </c>
     </row>
     <row r="16">
@@ -26362,10 +26312,10 @@
         <v>1.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>23.75</v>
+        <v>13.01333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -26373,13 +26323,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D17" t="n">
-        <v>16.38666666666667</v>
+        <v>31.26666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -26387,13 +26337,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D18" t="n">
-        <v>13.85333333333334</v>
+        <v>9.517741935483867</v>
       </c>
     </row>
     <row r="19">
@@ -26401,13 +26351,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>13.01333333333333</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20">
@@ -26415,13 +26365,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D20" t="n">
-        <v>31.26666666666667</v>
+        <v>21.13333333333334</v>
       </c>
     </row>
     <row r="21">
@@ -26429,13 +26379,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D21" t="n">
-        <v>9.517741935483867</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22">
@@ -26443,13 +26393,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D22" t="n">
-        <v>21.13333333333334</v>
+        <v>18.17666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -26460,10 +26410,10 @@
         <v>1.5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="n">
-        <v>18.17666666666667</v>
+        <v>12.40333333333334</v>
       </c>
     </row>
     <row r="24">
@@ -26471,13 +26421,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D24" t="n">
-        <v>12.40333333333334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25">
@@ -28530,22 +28480,22 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
     </row>
     <row r="2">
@@ -28553,23 +28503,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D2" t="n">
-        <v>6.504747899159661</v>
+        <v>7.19736842105263</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.266146179401996</v>
+        <v>1.755049833887043</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -28578,16 +28528,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D3" t="n">
-        <v>7.19736842105263</v>
+        <v>6.504747899159661</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -28595,7 +28545,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>1.755049833887043</v>
+        <v>2.266146179401996</v>
       </c>
     </row>
     <row r="4">
@@ -28603,16 +28553,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D4" t="n">
         <v>4.762785714285715</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -28628,16 +28578,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.597948290241866</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.011502919099264</v>
       </c>
       <c r="D5" t="n">
         <v>4.048206896551724</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -28653,19 +28603,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C6" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D6" t="n">
-        <v>2.266146179401996</v>
+        <v>1.755049833887043</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H6" t="n">
-        <v>6.504747899159661</v>
+        <v>7.19736842105263</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -28678,20 +28628,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C7" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D7" t="n">
-        <v>1.755049833887043</v>
+        <v>2.266146179401996</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>7.19736842105263</v>
+        <v>6.504747899159661</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -28709,7 +28659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28729,49 +28679,82 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.6</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.65</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.7</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>0.75</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>0.8</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>0.83</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>0.7887723102585491</v>
+        <v>0.95</v>
       </c>
       <c r="R1" s="1" t="n">
-        <v>0.8</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="S1" s="1" t="n">
-        <v>0.8021999999999969</v>
+        <v>1</v>
       </c>
       <c r="T1" s="1" t="n">
-        <v>1</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="U1" s="1" t="n">
+        <v>1.141816513761456</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>1.16944954128438</v>
+      </c>
+      <c r="X1" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="Y1" s="1" t="n">
+        <v>1.345900000000003</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA1" s="1" t="n">
         <v>1.4</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>1.575362802335276</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG1" s="1" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="2">
@@ -28779,16 +28762,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.45</v>
       </c>
       <c r="D2" t="n">
         <v>500</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -28803,10 +28786,21 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
         <v>500</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
         <v>500</v>
       </c>
     </row>
@@ -28815,16 +28809,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5</v>
       </c>
       <c r="D3" t="n">
         <v>76.3</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -28839,26 +28833,43 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
         <v>500</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6</v>
       </c>
       <c r="D4" t="n">
         <v>11.1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -28870,33 +28881,44 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>500</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>500</v>
       </c>
-      <c r="U4" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>8.25</v>
+        <v>500</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.575362802335276</v>
+        <v>0.8021999999999969</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -28907,30 +28929,41 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>1000</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="D6" t="n">
-        <v>500</v>
+        <v>230.3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -28941,30 +28974,49 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>500</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
         <v>500</v>
       </c>
+      <c r="AB6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
         <v>500</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.5</v>
+        <v>0.7887723102585491</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -28976,29 +29028,40 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>500</v>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>500</v>
+        <v>8.25</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.4</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -29007,72 +29070,98 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>500</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>500</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>49</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>15.67688022284123</v>
+      </c>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.4</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.7</v>
-      </c>
       <c r="D9" t="n">
-        <v>230.3</v>
+        <v>138.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="M9" t="n">
         <v>500</v>
       </c>
+      <c r="N9" t="n">
+        <v>250.8</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>52.8</v>
+      </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
         <v>500</v>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>138.4</v>
+        <v>250.8</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>1.345900000000003</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -29085,66 +29174,84 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>1000</v>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34.54830769230767</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D11" t="n">
-        <v>15.7</v>
+        <v>181.5407017543861</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1.2</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>500</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>34</v>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>33.74413793103447</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D12" t="n">
-        <v>500</v>
+        <v>70.2626050420168</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -29152,33 +29259,44 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>34.54830769230767</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>21.01428571428572</v>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.95</v>
       </c>
       <c r="C13" t="n">
-        <v>0.83</v>
+        <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>70.2626050420168</v>
+        <v>500</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.15</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -29187,32 +29305,43 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>181.5407017543861</v>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
-        <v>500</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.95</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.8</v>
       </c>
       <c r="D14" t="n">
-        <v>181.5407017543861</v>
+        <v>500</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -29223,7 +29352,7 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>15.67688022284123</v>
+        <v>70.2626050420168</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -29231,468 +29360,289 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C15" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D15" t="n">
         <v>21.01428571428572</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.4</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>33.74413793103447</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>138.4</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>15.7</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.597948290241866</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1.011502919099264</v>
+        <v>0.2</v>
       </c>
       <c r="D16" t="n">
-        <v>33.74413793103447</v>
+        <v>500</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
         <v>500</v>
       </c>
       <c r="I16" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>76.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11.1</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>52.8</v>
-      </c>
+      <c r="N16" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>500</v>
+      </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>500</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.598068390325265</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.16944954128438</v>
+        <v>0.4</v>
       </c>
       <c r="D17" t="n">
-        <v>34.54830769230767</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0.968371976647208</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>21.01428571428572</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+        <v>15.7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.6</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.75</v>
-      </c>
       <c r="D18" t="n">
-        <v>500</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H18" t="n">
-        <v>500</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>500</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+        <v>52.8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="D19" t="n">
-        <v>250.8</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>70.2626050420168</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+        <v>33.74413793103447</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D20" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>0.8231359466221788</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>181.5407017543861</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+        <v>15.67688022284123</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="I21" t="n">
-        <v>138.4</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>250.8</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C22" t="n">
-        <v>1.35</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D22" t="n">
-        <v>500</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>500</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+        <v>34.54830769230767</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="D23" t="n">
         <v>500</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.2</v>
       </c>
       <c r="C24" t="n">
-        <v>1.141816513761456</v>
+        <v>0.6</v>
       </c>
       <c r="D24" t="n">
-        <v>15.67688022284123</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>500</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7887723102585491</v>
+        <v>1.2</v>
       </c>
       <c r="C25" t="n">
-        <v>1.575362802335276</v>
+        <v>0.8</v>
       </c>
       <c r="D25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8</v>
+        <v>1.345900000000003</v>
       </c>
       <c r="C26" t="n">
-        <v>0.95</v>
+        <v>0.8021999999999969</v>
       </c>
       <c r="D26" t="n">
-        <v>500</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+        <v>1000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H27" t="n">
         <v>500</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="C28" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D28" t="n">
         <v>500</v>
@@ -29703,10 +29653,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="D29" t="n">
         <v>500</v>
@@ -29717,10 +29667,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C30" t="n">
         <v>0.8</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.6</v>
       </c>
       <c r="D30" t="n">
         <v>500</v>
@@ -29731,13 +29681,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8021999999999969</v>
+        <v>1.4</v>
       </c>
       <c r="C31" t="n">
-        <v>1.345900000000003</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1000</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
@@ -29745,10 +29695,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C32" t="n">
-        <v>1.15</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
         <v>500</v>
@@ -29759,13 +29709,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="C33" t="n">
         <v>1.4</v>
       </c>
       <c r="D33" t="n">
-        <v>49</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34">
@@ -29773,13 +29723,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>1.575362802335276</v>
       </c>
       <c r="C34" t="n">
-        <v>1.6</v>
+        <v>0.7887723102585491</v>
       </c>
       <c r="D34" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="35">
@@ -29787,10 +29737,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="C35" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="D35" t="n">
         <v>500</v>
@@ -29801,13 +29751,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="C36" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>17.4</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37">
@@ -29815,13 +29765,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C37" t="n">
         <v>1.2</v>
       </c>
-      <c r="C37" t="n">
-        <v>1.7</v>
-      </c>
       <c r="D37" t="n">
-        <v>500</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="38">
@@ -29829,10 +29779,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C38" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.8</v>
       </c>
       <c r="D38" t="n">
         <v>500</v>
@@ -29843,10 +29793,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C39" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="D39" t="n">
         <v>500</v>
@@ -29857,10 +29807,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C40" t="n">
         <v>1.4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1.8</v>
       </c>
       <c r="D40" t="n">
         <v>500</v>
@@ -30529,22 +30479,22 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
     </row>
     <row r="2">
@@ -30552,23 +30502,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D2" t="n">
-        <v>81.68067226890751</v>
+        <v>80.68631578947372</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>91.67873754152828</v>
+        <v>46.33720930232561</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -30577,16 +30527,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D3" t="n">
-        <v>80.68631578947372</v>
+        <v>81.68067226890751</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -30594,7 +30544,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>46.33720930232561</v>
+        <v>91.67873754152828</v>
       </c>
     </row>
     <row r="4">
@@ -30602,16 +30552,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D4" t="n">
         <v>87.22821428571416</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -30627,16 +30577,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.597948290241866</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.011502919099264</v>
       </c>
       <c r="D5" t="n">
         <v>83.64586206896514</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -30652,19 +30602,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C6" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D6" t="n">
-        <v>91.67873754152828</v>
+        <v>46.33720930232561</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H6" t="n">
-        <v>81.68067226890751</v>
+        <v>80.68631578947372</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -30677,20 +30627,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C7" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D7" t="n">
-        <v>46.33720930232561</v>
+        <v>91.67873754152828</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>80.68631578947372</v>
+        <v>81.68067226890751</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -30728,22 +30678,22 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
     </row>
     <row r="2">
@@ -30751,23 +30701,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D2" t="n">
-        <v>15.53025210084034</v>
+        <v>28.01789473684211</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>8.180398671096341</v>
+        <v>4.904983388704308</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -30776,16 +30726,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D3" t="n">
-        <v>28.01789473684211</v>
+        <v>15.53025210084034</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -30793,7 +30743,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>4.904983388704308</v>
+        <v>8.180398671096341</v>
       </c>
     </row>
     <row r="4">
@@ -30801,16 +30751,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D4" t="n">
         <v>7.865357142857137</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -30826,16 +30776,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.597948290241866</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.011502919099264</v>
       </c>
       <c r="D5" t="n">
         <v>10.2741379310345</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -30851,19 +30801,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C6" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D6" t="n">
-        <v>8.180398671096341</v>
+        <v>4.904983388704308</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H6" t="n">
-        <v>15.53025210084034</v>
+        <v>28.01789473684211</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -30876,20 +30826,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C7" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D7" t="n">
-        <v>4.904983388704308</v>
+        <v>8.180398671096341</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>28.01789473684211</v>
+        <v>15.53025210084034</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -30927,22 +30877,22 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
     </row>
     <row r="2">
@@ -30950,23 +30900,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D2" t="n">
-        <v>97.2109243697479</v>
+        <v>108.7042105263159</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>99.85913621262455</v>
+        <v>51.2421926910298</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -30975,16 +30925,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D3" t="n">
-        <v>108.7042105263159</v>
+        <v>97.2109243697479</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -30992,7 +30942,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>51.2421926910298</v>
+        <v>99.85913621262455</v>
       </c>
     </row>
     <row r="4">
@@ -31000,16 +30950,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D4" t="n">
         <v>95.09357142857144</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -31025,16 +30975,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.597948290241866</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.011502919099264</v>
       </c>
       <c r="D5" t="n">
         <v>93.92000000000002</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -31050,19 +31000,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C6" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D6" t="n">
-        <v>99.85913621262455</v>
+        <v>51.2421926910298</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H6" t="n">
-        <v>97.2109243697479</v>
+        <v>108.7042105263159</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -31075,20 +31025,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C7" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D7" t="n">
-        <v>51.2421926910298</v>
+        <v>99.85913621262455</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>108.7042105263159</v>
+        <v>97.2109243697479</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -31106,7 +31056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31126,46 +31076,79 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.6</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.65</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.7</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>0.75</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>0.8</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>0.83</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="R1" s="1" t="n">
-        <v>0.8021999999999969</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="S1" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T1" s="1" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>1.141816513761456</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>1.16944954128438</v>
+      </c>
+      <c r="X1" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="Y1" s="1" t="n">
+        <v>1.345900000000003</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA1" s="1" t="n">
         <v>1.4</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="2">
@@ -31173,16 +31156,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.45</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -31196,10 +31179,21 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
         <v>15</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -31208,16 +31202,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5</v>
       </c>
       <c r="D3" t="n">
         <v>7.76</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -31231,26 +31225,43 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="AE3" t="n">
         <v>15</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6</v>
       </c>
       <c r="D4" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -31261,33 +31272,44 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
         <v>15</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
         <v>15</v>
       </c>
-      <c r="T4" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>12.82</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.55</v>
+        <v>0.8021999999999969</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -31302,25 +31324,36 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
         <v>15</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>9.41</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -31332,28 +31365,47 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.4</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -31362,70 +31414,96 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>15</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>14.44</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>15</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>14.29531561461795</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>12.82</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>15</v>
-      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>9</v>
-      </c>
+      <c r="S8" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.4</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.7</v>
-      </c>
       <c r="D9" t="n">
-        <v>9.41</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1.345900000000003</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -31437,65 +31515,83 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>15</v>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>13.65129568106314</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>9.630000000000001</v>
+        <v>11.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>1.2</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>15</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>14.02</v>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>11.77</v>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>12.56541379310344</v>
+      </c>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D11" t="n">
-        <v>12.96</v>
+        <v>10.17792982456142</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -31503,32 +31599,43 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>13.65129568106314</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>11.99239285714287</v>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>10.35621848739495</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1.15</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -31537,31 +31644,42 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>10.17792982456142</v>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>8</v>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>0.4051426188490391</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D13" t="n">
-        <v>10.35621848739495</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>1.141816513761456</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -31572,465 +31690,297 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>14.29531561461795</v>
+        <v>10.35621848739495</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.95</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.8</v>
       </c>
       <c r="D14" t="n">
-        <v>10.17792982456142</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.4</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>12.56541379310344</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>9.630000000000001</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>12.96</v>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C15" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D15" t="n">
         <v>11.99239285714287</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>7.76</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9.880000000000001</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>12.46</v>
-      </c>
+      <c r="N15" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>15</v>
+      </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.597948290241866</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1.011502919099264</v>
+        <v>0.2</v>
       </c>
       <c r="D16" t="n">
-        <v>12.56541379310344</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>0.968371976647208</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>11.99239285714287</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.598068390325265</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.16944954128438</v>
+        <v>0.4</v>
       </c>
       <c r="D17" t="n">
-        <v>13.65129568106314</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>10</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+        <v>12.96</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.6</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.75</v>
-      </c>
       <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>10.35621848739495</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+        <v>12.46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="D19" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0.8231359466221788</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>10.17792982456142</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+        <v>12.56541379310344</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D20" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+        <v>14.29531561461795</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C22" t="n">
-        <v>1.35</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+        <v>13.65129568106314</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.2</v>
       </c>
       <c r="C24" t="n">
-        <v>1.141816513761456</v>
+        <v>0.6</v>
       </c>
       <c r="D24" t="n">
-        <v>14.29531561461795</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+        <v>14.02</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C25" t="n">
         <v>0.8</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.95</v>
-      </c>
       <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+        <v>11.77</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8</v>
+        <v>1.345900000000003</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2</v>
+        <v>0.8021999999999969</v>
       </c>
       <c r="D26" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H26" t="n">
-        <v>7</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
-        <v>14.44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -32038,13 +31988,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="C28" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -32052,10 +32002,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="C29" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
@@ -32066,13 +32016,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8021999999999969</v>
+        <v>1.4</v>
       </c>
       <c r="C30" t="n">
-        <v>1.345900000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="31">
@@ -32080,13 +32030,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="C31" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -32094,10 +32044,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
@@ -32108,10 +32058,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="C33" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
@@ -32122,13 +32072,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="C34" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -32136,13 +32086,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="C35" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>14.81</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -32150,13 +32100,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C36" t="n">
         <v>1.2</v>
       </c>
-      <c r="C36" t="n">
-        <v>1.7</v>
-      </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="37">
@@ -32164,10 +32114,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C37" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1.8</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
@@ -32178,10 +32128,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C38" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
@@ -32192,10 +32142,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C39" t="n">
         <v>1.4</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1.8</v>
       </c>
       <c r="D39" t="n">
         <v>15</v>
@@ -32232,22 +32182,22 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
     </row>
     <row r="2">
@@ -32255,23 +32205,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D2" t="n">
-        <v>93.14285714285714</v>
+        <v>81.80350877192983</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>130.7873754152824</v>
+        <v>131.9800664451827</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -32280,16 +32230,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D3" t="n">
-        <v>81.80350877192983</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -32297,7 +32247,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>131.9800664451827</v>
+        <v>130.7873754152824</v>
       </c>
     </row>
     <row r="4">
@@ -32305,16 +32255,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D4" t="n">
         <v>116.0642857142857</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -32330,16 +32280,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.597948290241866</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.011502919099264</v>
       </c>
       <c r="D5" t="n">
         <v>113.8172413793103</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -32355,19 +32305,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C6" t="n">
-        <v>1.16944954128438</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D6" t="n">
-        <v>130.7873754152824</v>
+        <v>131.9800664451827</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.83</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H6" t="n">
-        <v>93.14285714285714</v>
+        <v>81.80350877192983</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -32380,20 +32330,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C7" t="n">
-        <v>1.141816513761456</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D7" t="n">
-        <v>131.9800664451827</v>
+        <v>130.7873754152824</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>81.80350877192983</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -39764,7 +39714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39825,7 +39775,7 @@
         <v>0.51</v>
       </c>
       <c r="C2" t="n">
-        <v>1.44</v>
+        <v>0.51</v>
       </c>
       <c r="D2" t="n">
         <v>750</v>
@@ -39834,14 +39784,14 @@
         <v>0.51</v>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>750</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>750</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -39855,7 +39805,7 @@
         <v>0.76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="D3" t="n">
         <v>750</v>
@@ -39863,14 +39813,14 @@
       <c r="G3" s="1" t="n">
         <v>0.76</v>
       </c>
-      <c r="H3" t="n">
-        <v>750</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>750</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -39882,13 +39832,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="D4" t="n">
-        <v>750</v>
+        <v>79.33998623537506</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>0.9</v>
@@ -39897,7 +39847,9 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>750</v>
+      </c>
       <c r="M4" t="n">
         <v>104.4608186819114</v>
       </c>
@@ -39921,10 +39873,10 @@
         <v>0.9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>79.33998623537506</v>
+        <v>750</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>0.99</v>
@@ -39932,10 +39884,10 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
         <v>750</v>
       </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -39960,10 +39912,10 @@
         <v>1.03</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
         <v>750</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -39990,7 +39942,9 @@
         <v>1.44</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>750</v>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>51.57648061354919</v>
@@ -40007,14 +39961,16 @@
       <c r="Q7" t="n">
         <v>38.96997069057129</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="C8" t="n">
         <v>0.99</v>
@@ -40025,7 +39981,9 @@
       <c r="G8" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>750</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>79.33998623537506</v>
@@ -40044,7 +40002,9 @@
       <c r="P8" t="n">
         <v>46.24586217273549</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>750</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -40052,13 +40012,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="C9" t="n">
         <v>1.03</v>
       </c>
       <c r="D9" t="n">
-        <v>104.4608186819114</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10">
@@ -40066,13 +40026,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.51</v>
+        <v>1.03</v>
       </c>
       <c r="D10" t="n">
-        <v>39.83499272849312</v>
+        <v>104.4608186819114</v>
       </c>
     </row>
     <row r="11">
@@ -40080,13 +40040,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.76</v>
+        <v>1.44</v>
       </c>
       <c r="D11" t="n">
-        <v>38.90992835209825</v>
+        <v>750</v>
       </c>
     </row>
     <row r="12">
@@ -40097,10 +40057,10 @@
         <v>1.11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.03</v>
+        <v>0.51</v>
       </c>
       <c r="D12" t="n">
-        <v>56.09510453850078</v>
+        <v>39.83499272849312</v>
       </c>
     </row>
     <row r="13">
@@ -40108,13 +40068,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="D13" t="n">
-        <v>40.28187386569873</v>
+        <v>38.90992835209825</v>
       </c>
     </row>
     <row r="14">
@@ -40122,13 +40082,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="D14" t="n">
-        <v>34.64110157848134</v>
+        <v>56.09510453850078</v>
       </c>
     </row>
     <row r="15">
@@ -40136,13 +40096,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="C15" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="n">
-        <v>27.58086167220658</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16">
@@ -40150,13 +40110,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="C16" t="n">
         <v>0.51</v>
       </c>
       <c r="D16" t="n">
-        <v>46.24586217273549</v>
+        <v>40.28187386569873</v>
       </c>
     </row>
     <row r="17">
@@ -40164,13 +40124,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="C17" t="n">
         <v>0.76</v>
       </c>
       <c r="D17" t="n">
-        <v>38.96997069057129</v>
+        <v>34.64110157848134</v>
       </c>
     </row>
     <row r="18">
@@ -40178,12 +40138,82 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="C18" t="n">
         <v>1.03</v>
       </c>
       <c r="D18" t="n">
+        <v>27.58086167220658</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D19" t="n">
+        <v>46.24586217273549</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D20" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>38.96997069057129</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D22" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D23" t="n">
         <v>28.71403571495777</v>
       </c>
     </row>
@@ -40494,7 +40524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40514,45 +40544,33 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R1" s="1" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S1" s="1" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T1" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U1" s="1" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -40561,13 +40579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.44</v>
-      </c>
       <c r="D2" t="n">
-        <v>750</v>
+        <v>122.9820934753442</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>0.4</v>
@@ -40578,26 +40596,32 @@
         <v>750</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>67.09223818467945</v>
+      </c>
+      <c r="M2" t="n">
+        <v>21.91179405308322</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14.91524186119661</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>17.40882059386177</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>20.34221024817367</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9</v>
       </c>
       <c r="D3" t="n">
         <v>750</v>
@@ -40609,31 +40633,37 @@
       <c r="I3" t="n">
         <v>750</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>82.9507330603619</v>
+      </c>
+      <c r="K3" t="n">
+        <v>48.68781149177096</v>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>19.88495603449193</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>22.20015741905133</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>750</v>
+        <v>61.33424223442277</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>0.8</v>
@@ -40641,237 +40671,134 @@
       <c r="H4" t="n">
         <v>750</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>102.9277941295601</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>47.87963990778125</v>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>22.67783370408718</v>
+      </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>26.16758997688668</v>
+      </c>
+      <c r="P4" t="n">
+        <v>750</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="C5" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="D5" t="n">
+        <v>102.9277941295601</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>122.9820934753442</v>
+      </c>
+      <c r="I5" t="n">
+        <v>61.33424223442277</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>41.81214100687014</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>31.29191144524832</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.66530437420806</v>
+      </c>
+      <c r="O5" t="n">
         <v>750</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>67.09223818467945</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21.91179405308322</v>
-      </c>
-      <c r="R5" t="n">
-        <v>14.91524186119661</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>17.40882059386177</v>
-      </c>
-      <c r="U5" t="n">
-        <v>20.34221024817367</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.65</v>
       </c>
       <c r="D6" t="n">
         <v>750</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>750</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
-        <v>122.9820934753442</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>750</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>82.9507330603619</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="n">
-        <v>61.33424223442277</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
         <v>750</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D9" t="n">
-        <v>102.9277941295601</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>82.9507330603619</v>
-      </c>
-      <c r="N9" t="n">
-        <v>48.68781149177096</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>19.88495603449193</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>22.20015741905133</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>41.81214100687014</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>82.9507330603619</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>102.9277941295601</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
         <v>47.87963990778125</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>22.67783370408718</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>26.16758997688668</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -40881,51 +40808,24 @@
         <v>1.11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D11" t="n">
-        <v>41.81214100687014</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>122.9820934753442</v>
-      </c>
-      <c r="L11" t="n">
-        <v>61.33424223442277</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>41.81214100687014</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>31.29191144524832</v>
-      </c>
-      <c r="R11" t="n">
-        <v>37.66530437420806</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+        <v>48.68781149177096</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D12" t="n">
-        <v>47.87963990778125</v>
+        <v>67.09223818467945</v>
       </c>
     </row>
     <row r="13">
@@ -40933,13 +40833,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D13" t="n">
-        <v>48.68781149177096</v>
+        <v>31.29191144524832</v>
       </c>
     </row>
     <row r="14">
@@ -40947,13 +40847,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="C14" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="D14" t="n">
-        <v>750</v>
+        <v>22.67783370408718</v>
       </c>
     </row>
     <row r="15">
@@ -40961,13 +40861,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D15" t="n">
-        <v>67.09223818467945</v>
+        <v>19.88495603449193</v>
       </c>
     </row>
     <row r="16">
@@ -40978,10 +40878,10 @@
         <v>1.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>31.29191144524832</v>
+        <v>21.91179405308322</v>
       </c>
     </row>
     <row r="17">
@@ -40989,13 +40889,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D17" t="n">
-        <v>22.67783370408718</v>
+        <v>37.66530437420806</v>
       </c>
     </row>
     <row r="18">
@@ -41003,13 +40903,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D18" t="n">
-        <v>19.88495603449193</v>
+        <v>14.91524186119661</v>
       </c>
     </row>
     <row r="19">
@@ -41017,13 +40917,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>21.91179405308322</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20">
@@ -41031,13 +40931,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D20" t="n">
-        <v>37.66530437420806</v>
+        <v>26.16758997688668</v>
       </c>
     </row>
     <row r="21">
@@ -41045,13 +40945,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D21" t="n">
-        <v>14.91524186119661</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22">
@@ -41059,13 +40959,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D22" t="n">
-        <v>26.16758997688668</v>
+        <v>22.20015741905133</v>
       </c>
     </row>
     <row r="23">
@@ -41076,10 +40976,10 @@
         <v>1.5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="n">
-        <v>22.20015741905133</v>
+        <v>17.40882059386177</v>
       </c>
     </row>
     <row r="24">
@@ -41087,13 +40987,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D24" t="n">
-        <v>17.40882059386177</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25">
@@ -41522,7 +41422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41542,49 +41442,82 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.6</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.65</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.7</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>0.75</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>0.8</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>0.6</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>0.83</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>0.7887723102585491</v>
+        <v>0.95</v>
       </c>
       <c r="R1" s="1" t="n">
-        <v>0.8</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="S1" s="1" t="n">
-        <v>0.8021999999999969</v>
+        <v>1</v>
       </c>
       <c r="T1" s="1" t="n">
-        <v>1</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="U1" s="1" t="n">
+        <v>1.141816513761456</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>1.16944954128438</v>
+      </c>
+      <c r="X1" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="Y1" s="1" t="n">
+        <v>1.345900000000003</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA1" s="1" t="n">
         <v>1.4</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>1.575362802335276</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG1" s="1" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="2">
@@ -41592,16 +41525,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.45</v>
       </c>
       <c r="D2" t="n">
         <v>750</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -41616,10 +41549,21 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
         <v>750</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
         <v>750</v>
       </c>
     </row>
@@ -41628,16 +41572,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5</v>
       </c>
       <c r="D3" t="n">
         <v>750</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -41652,26 +41596,43 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
         <v>750</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>750</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>750</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6</v>
       </c>
       <c r="D4" t="n">
         <v>750</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.6</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -41683,33 +41644,44 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>750</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
         <v>750</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>750</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D5" t="n">
         <v>750</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.65</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -41720,30 +41692,41 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>750</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>750</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="D6" t="n">
         <v>750</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.7</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -41754,30 +41737,49 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>750</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
         <v>750</v>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>750</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>750</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>750</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
         <v>750</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.75</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -41789,29 +41791,40 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>750</v>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>750</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="n">
         <v>750</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.8</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -41820,72 +41833,98 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>750</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>750</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>750</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>18.3284343149417</v>
+      </c>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7</v>
       </c>
       <c r="D9" t="n">
         <v>750</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="M9" t="n">
         <v>750</v>
       </c>
+      <c r="N9" t="n">
+        <v>750</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>750</v>
+      </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
         <v>750</v>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>750</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>750</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
         <v>750</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.83</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -41898,66 +41937,84 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>750</v>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>41.49370068331777</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.4952627189324375</v>
       </c>
       <c r="D11" t="n">
-        <v>750</v>
+        <v>295.9338417540517</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.95</v>
+        <v>0.7887723102585491</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>750</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>750</v>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>750</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>44.78836538500657</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2</v>
+        <v>0.4051426188490391</v>
       </c>
       <c r="D12" t="n">
-        <v>750</v>
+        <v>109.063892262607</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -41965,33 +42022,44 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>41.49370068331777</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>29.11961499377534</v>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.95</v>
       </c>
       <c r="C13" t="n">
-        <v>0.83</v>
+        <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>109.063892262607</v>
+        <v>750</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1</v>
+        <v>0.8021999999999969</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -42000,32 +42068,43 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>295.9338417540517</v>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
-        <v>750</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.95</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8231359466221788</v>
+        <v>0.8</v>
       </c>
       <c r="D14" t="n">
-        <v>295.9338417540517</v>
+        <v>750</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -42036,7 +42115,7 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>18.3284343149417</v>
+        <v>109.063892262607</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -42044,56 +42123,86 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C15" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D15" t="n">
         <v>29.11961499377534</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.141816513761456</v>
+        <v>1.2</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>44.78836538500657</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>750</v>
+      </c>
+      <c r="L15" t="n">
+        <v>750</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>750</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>750</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.597948290241866</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1.011502919099264</v>
+        <v>0.2</v>
       </c>
       <c r="D16" t="n">
-        <v>44.78836538500657</v>
+        <v>750</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="H16" t="n">
         <v>750</v>
@@ -42101,411 +42210,202 @@
       <c r="I16" t="n">
         <v>750</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>750</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="N16" t="n">
         <v>750</v>
       </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>750</v>
+      </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>750</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.598068390325265</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.16944954128438</v>
+        <v>0.4</v>
       </c>
       <c r="D17" t="n">
-        <v>41.49370068331777</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>1.16944954128438</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>29.11961499377534</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+        <v>750</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.75</v>
       </c>
       <c r="D18" t="n">
         <v>750</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>750</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>750</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="D19" t="n">
-        <v>750</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>1.345900000000003</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>109.063892262607</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+        <v>44.78836538500657</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.7047522935779692</v>
       </c>
       <c r="D20" t="n">
-        <v>750</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>295.9338417540517</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+        <v>18.3284343149417</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>750</v>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>750</v>
-      </c>
-      <c r="I21" t="n">
-        <v>750</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>750</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>1.16944954128438</v>
       </c>
       <c r="C22" t="n">
-        <v>1.35</v>
+        <v>0.598068390325265</v>
       </c>
       <c r="D22" t="n">
-        <v>750</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>750</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+        <v>41.49370068331777</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="D23" t="n">
         <v>750</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>750</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.2</v>
       </c>
       <c r="C24" t="n">
-        <v>1.141816513761456</v>
+        <v>0.6</v>
       </c>
       <c r="D24" t="n">
-        <v>18.3284343149417</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>1.575362802335276</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
         <v>750</v>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7887723102585491</v>
+        <v>1.2</v>
       </c>
       <c r="C25" t="n">
-        <v>1.575362802335276</v>
+        <v>0.8</v>
       </c>
       <c r="D25" t="n">
         <v>750</v>
       </c>
-      <c r="G25" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>750</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8</v>
+        <v>1.345900000000003</v>
       </c>
       <c r="C26" t="n">
-        <v>0.95</v>
+        <v>0.8021999999999969</v>
       </c>
       <c r="D26" t="n">
         <v>750</v>
       </c>
-      <c r="G26" s="1" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>750</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
         <v>750</v>
       </c>
-      <c r="G27" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>750</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="C28" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D28" t="n">
         <v>750</v>
@@ -42516,10 +42416,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="D29" t="n">
         <v>750</v>
@@ -42530,10 +42430,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C30" t="n">
         <v>0.8</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.6</v>
       </c>
       <c r="D30" t="n">
         <v>750</v>
@@ -42544,10 +42444,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8021999999999969</v>
+        <v>1.4</v>
       </c>
       <c r="C31" t="n">
-        <v>1.345900000000003</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>750</v>
@@ -42558,10 +42458,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C32" t="n">
-        <v>1.15</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
         <v>750</v>
@@ -42572,7 +42472,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="C33" t="n">
         <v>1.4</v>
@@ -42586,10 +42486,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>1.575362802335276</v>
       </c>
       <c r="C34" t="n">
-        <v>1.6</v>
+        <v>0.7887723102585491</v>
       </c>
       <c r="D34" t="n">
         <v>750</v>
@@ -42600,10 +42500,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="C35" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="D35" t="n">
         <v>750</v>
@@ -42614,10 +42514,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="C36" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>750</v>
@@ -42628,10 +42528,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C37" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1.7</v>
       </c>
       <c r="D37" t="n">
         <v>750</v>
@@ -42642,10 +42542,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C38" t="n">
         <v>1.2</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.8</v>
       </c>
       <c r="D38" t="n">
         <v>750</v>
@@ -42656,10 +42556,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C39" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="D39" t="n">
         <v>750</v>
@@ -42670,10 +42570,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C40" t="n">
         <v>1.4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1.8</v>
       </c>
       <c r="D40" t="n">
         <v>750</v>
@@ -43342,22 +43242,22 @@
         </is>
       </c>
       <c r="H1" s="1" t="n">
-        <v>0.4051426188490391</v>
+        <v>0.8231359466221788</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>0.4952627189324375</v>
+        <v>0.83</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>0.5317180984153469</v>
+        <v>0.968371976647208</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>0.597948290241866</v>
+        <v>1.011502919099264</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>0.598068390325265</v>
+        <v>1.141816513761456</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>0.7047522935779692</v>
+        <v>1.16944954128438</v>
       </c>
     </row>
     <row r="2">
@@ -43365,23 +43265,23 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0.8231359466221788</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4952627189324375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>290.6101887511917</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>0.4051426188490391</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D2" t="n">
-        <v>247.466072634621</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.8231359466221788</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>196.6921574990822</v>
+        <v>98.2510681492144</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -43390,16 +43290,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4051426188490391</v>
+      </c>
+      <c r="D3" t="n">
+        <v>247.466072634621</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>0.4952627189324375</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8231359466221788</v>
-      </c>
-      <c r="D3" t="n">
-        <v>290.6101887511917</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.83</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -43407,7 +43307,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>98.2510681492144</v>
+        <v>196.6921574990822</v>
       </c>
     </row>
     <row r="4">
@@ -43415,16 +43315,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.968371976647208</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5317180984153469</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.968371976647208</v>
       </c>
       <c r="D4" t="n">
         <v>216.1055907725199</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.968371976647208</v>
+        <v>0.5317180984153469</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -43440,16 +43340,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>1.011502919099264</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.597948290241866</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.011502919099264</v>
       </c>
       <c r="D5" t="n">
         <v>204.4413814427118</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.011502919099264</v>
+        <v>0.597948290241866</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -43465,19 +43365,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>1.141816513761456</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7047522935779692</v>
+      </c>
+      <c r="D6" t="n">
+        <v>98.2510681492144</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>0.598068390325265</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.16944954128438</v>
-      </c>
-      <c r="D6" t="n">
-        <v>196.6921574990822</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1.141816513761456</v>
-      </c>
       <c r="H6" t="n">
-        <v>247.466072634621</v>
+        <v>290.6101887511917</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -43490,20 +43390,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>1.16944954128438</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.598068390325265</v>
+      </c>
+      <c r="D7" t="n">
+        <v>196.6921574990822</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>0.7047522935779692</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.141816513761456</v>
-      </c>
-      <c r="D7" t="n">
-        <v>98.2510681492144</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1.16944954128438</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>290.6101887511917</v>
+        <v>247.466072634621</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
